--- a/dino.xlsx
+++ b/dino.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/y_f_bats_uu_nl/Documents/Documents/PhD/FluxModel/Rebuttal PP/GitHub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="11_92373ED78F79A8D366075C52F37BD2726AC1AA26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E16FED-20D7-47CA-BB2E-0AF4F1C10150}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_92373ED78F79A8D366075C52F37BD2726AC1AA26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C381CDA-16E3-4898-8D8B-E5E667229477}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,9 +102,6 @@
     <t>h</t>
   </si>
   <si>
-    <t>μmol/L</t>
-  </si>
-  <si>
     <t>cm^3</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>10.1371/journal.pone.0154370</t>
+  </si>
+  <si>
+    <t>μmol/kg</t>
   </si>
 </sst>
 </file>
@@ -549,7 +549,7 @@
         <v>18</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -590,7 +590,7 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -631,7 +631,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -672,7 +672,7 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -713,7 +713,7 @@
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -754,7 +754,7 @@
         <v>20</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -795,7 +795,7 @@
         <v>20</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -836,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="M8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -877,7 +877,7 @@
         <v>20</v>
       </c>
       <c r="M9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -918,7 +918,7 @@
         <v>20</v>
       </c>
       <c r="M10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -959,7 +959,7 @@
         <v>20</v>
       </c>
       <c r="M11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -1000,7 +1000,7 @@
         <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1041,7 +1041,7 @@
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1082,7 +1082,7 @@
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -1123,7 +1123,7 @@
         <v>19</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -1164,7 +1164,7 @@
         <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
@@ -1205,7 +1205,7 @@
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
@@ -1246,7 +1246,7 @@
         <v>19</v>
       </c>
       <c r="M18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
@@ -1287,7 +1287,7 @@
         <v>19</v>
       </c>
       <c r="M19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
@@ -1328,7 +1328,7 @@
         <v>19</v>
       </c>
       <c r="M20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
@@ -1369,7 +1369,7 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
@@ -1410,7 +1410,7 @@
         <v>19</v>
       </c>
       <c r="M22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
@@ -1448,10 +1448,10 @@
         <v>10</v>
       </c>
       <c r="L23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -1489,10 +1489,10 @@
         <v>10</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -1530,10 +1530,10 @@
         <v>10</v>
       </c>
       <c r="L25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
@@ -1571,10 +1571,10 @@
         <v>11</v>
       </c>
       <c r="L26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
@@ -1612,10 +1612,10 @@
         <v>11</v>
       </c>
       <c r="L27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
@@ -1653,10 +1653,10 @@
         <v>11</v>
       </c>
       <c r="L28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1707,28 +1707,28 @@
         <v>21</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
